--- a/Analysis/Sensitivity_alpha_sweep_deepseek.xlsx
+++ b/Analysis/Sensitivity_alpha_sweep_deepseek.xlsx
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.32786</v>
+        <v>0.30668</v>
       </c>
       <c r="G3" t="n">
-        <v>0.35384</v>
+        <v>0.33078</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5446</v>
+        <v>0.5353800000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8154</v>
+        <v>0.8112999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>195</v>
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.89734</v>
+        <v>0.89732</v>
       </c>
       <c r="G4" t="n">
         <v>0.9101399999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.90762</v>
+        <v>0.9076000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>0.9774200000000001</v>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.124</v>
+        <v>0.12676</v>
       </c>
       <c r="G5" t="n">
-        <v>0.12766</v>
+        <v>0.12972</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3503</v>
+        <v>0.35444</v>
       </c>
       <c r="I5" t="n">
         <v>0.7149</v>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.32514</v>
+        <v>0.3169400000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3492400000000001</v>
+        <v>0.34052</v>
       </c>
       <c r="H6" t="n">
-        <v>0.53744</v>
+        <v>0.54052</v>
       </c>
       <c r="I6" t="n">
-        <v>0.81024</v>
+        <v>0.8122999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>195</v>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.88498</v>
+        <v>0.88842</v>
       </c>
       <c r="G7" t="n">
-        <v>0.90144</v>
+        <v>0.9039999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8973199999999999</v>
+        <v>0.9024599999999999</v>
       </c>
       <c r="I7" t="n">
         <v>0.9815200000000001</v>
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.3258</v>
+        <v>0.31008</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3513</v>
+        <v>0.3333199999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5425800000000001</v>
+        <v>0.5405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.81232</v>
+        <v>0.8112999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>195</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.9007400000000001</v>
+        <v>0.90076</v>
       </c>
       <c r="G10" t="n">
         <v>0.9153</v>
@@ -847,16 +847,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.144</v>
+        <v>0.1419</v>
       </c>
       <c r="G11" t="n">
-        <v>0.14522</v>
+        <v>0.14366</v>
       </c>
       <c r="H11" t="n">
-        <v>0.36682</v>
+        <v>0.36472</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7221</v>
+        <v>0.72106</v>
       </c>
       <c r="J11" t="n">
         <v>193.6</v>
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.32786</v>
+        <v>0.30872</v>
       </c>
       <c r="G12" t="n">
-        <v>0.35384</v>
+        <v>0.3322999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5446</v>
+        <v>0.53844</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8154</v>
+        <v>0.8112999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>195</v>
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.89734</v>
+        <v>0.90076</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9101399999999999</v>
+        <v>0.9153</v>
       </c>
       <c r="H13" t="n">
-        <v>0.90762</v>
+        <v>0.91272</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9774200000000001</v>
+        <v>0.98254</v>
       </c>
       <c r="J13" t="n">
         <v>194.8</v>
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.15294</v>
+        <v>0.15088</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1566</v>
+        <v>0.15504</v>
       </c>
       <c r="H14" t="n">
-        <v>0.37198</v>
+        <v>0.36992</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7252000000000001</v>
+        <v>0.72416</v>
       </c>
       <c r="J14" t="n">
         <v>193.6</v>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.32992</v>
+        <v>0.30394</v>
       </c>
       <c r="G15" t="n">
-        <v>0.35542</v>
+        <v>0.32562</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5446199999999999</v>
+        <v>0.53846</v>
       </c>
       <c r="I15" t="n">
-        <v>0.81232</v>
+        <v>0.8082</v>
       </c>
       <c r="J15" t="n">
         <v>195</v>
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.8884400000000001</v>
+        <v>0.89186</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9035</v>
+        <v>0.9086399999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.90244</v>
+        <v>0.9076000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9774200000000001</v>
+        <v>0.98254</v>
       </c>
       <c r="J16" t="n">
         <v>194.8</v>
